--- a/etf_holdings/2026-10-29_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.04%2425</t>
+          <t>-0.41%2415</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2425</v>
+        <v>2415</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.07%1,544,000</t>
+          <t>8.14%1,609,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.07%</t>
+          <t>8.14%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1544000</v>
+        <v>1609000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+6.94%4235</t>
+          <t>-4.49%4045</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+6.94%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4235</v>
+        <v>4045</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.78%786,000</t>
+          <t>6.95%786,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.78%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+9.98%540</t>
+          <t>+10%594</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>540</v>
+        <v>594</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.10%5,709,000</t>
+          <t>6.43%5,709,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.10%</t>
+          <t>6.43%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+3.22%673</t>
+          <t>-1.19%665</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+3.22%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.32%3,745,000</t>
+          <t>5.26%3,745,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+3.56%843</t>
+          <t>-0.24%841</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+3.56%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.08%2,300,000</t>
+          <t>4.05%2,300,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.09%2035</t>
+          <t>-4.42%1945</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+4.09%</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2035</v>
+        <v>1945</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.05%951,000</t>
+          <t>4.04%951,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5.77%550</t>
+          <t>-5.45%520</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+5.77%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.58%3,158,000</t>
+          <t>3.63%3,158,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+5.58%6335</t>
+          <t>-8.21%5815</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+5.58%</t>
+          <t>-8.21%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6335</v>
+        <v>5815</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.31%253,000</t>
+          <t>3.35%253,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.1%1340</t>
+          <t>-3.73%1290</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>-3.73%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1340</v>
+        <v>1290</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.28%1,180,000</t>
+          <t>3.30%1,180,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5.79%5025</t>
+          <t>-0.3%5010</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5025</v>
+        <v>5010</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.20%309,000</t>
+          <t>3.24%309,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+6.78%5115</t>
+          <t>-5.38%4840</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+6.78%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5115</v>
+        <v>4840</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.14%301,000</t>
+          <t>3.21%301,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%1950</t>
+          <t>-2.66%9880</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1950</v>
+        <v>9880</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.87%676,225</t>
+          <t>2.73%129,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>676225</v>
+        <v>129000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+3.47%10150</t>
+          <t>-3.42%3105</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+3.47%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>10150</v>
+        <v>3105</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.76%129,000</t>
+          <t>2.51%374,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>129000</v>
+        <v>374000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.72%3215</t>
+          <t>-3.33%1885</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.72%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3215</v>
+        <v>1885</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.55%374,000</t>
+          <t>2.41%592,225</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>374000</v>
+        <v>592225</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:53</t>
+          <t>2026-10-29 23:20:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.1%194.5</t>
+          <t>-3.08%188.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>194.5</v>
+        <v>188.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.01%4,838,000</t>
+          <t>1.96%4,838,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+4.3%849</t>
+          <t>-4.12%814</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>-4.12%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>849</v>
+        <v>814</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+3.56%261.5</t>
+          <t>-3.63%252</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+3.56%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>261.5</v>
+        <v>252</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.78%3,234,000</t>
+          <t>1.76%3,234,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.38%221</t>
+          <t>-5.47%484</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-5.47%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>221</v>
+        <v>484</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.60%3,364,000</t>
+          <t>1.64%1,539,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3364000</v>
+        <v>1539000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+9.87%512</t>
+          <t>-4.07%212</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+9.87%</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>512</v>
+        <v>212</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.56%1,539,000</t>
+          <t>1.55%3,364,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1539000</v>
+        <v>3364000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.29%778</t>
+          <t>-4.24%745</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.23%200.5</t>
+          <t>+0.75%202</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>+0.75%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>200.5</v>
+        <v>202</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.52%3,438,000</t>
+          <t>1.44%3,438,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.29%689</t>
+          <t>-2.32%673</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-2.32%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.44%964,000</t>
+          <t>1.39%964,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+2.17%188.5</t>
+          <t>-1.73%683</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>188.5</v>
+        <v>683</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.38%3,439,000</t>
+          <t>1.38%954,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3439000</v>
+        <v>954000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.49%128</t>
+          <t>+0.71%566</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.49%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>128</v>
+        <v>566</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.37%5,153,000</t>
+          <t>1.38%1,175,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>5153000</v>
+        <v>1175000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+5.44%562</t>
+          <t>-9.77%115.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>562</v>
+        <v>115.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.36%1,175,000</t>
+          <t>1.38%5,153,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1175000</v>
+        <v>5153000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.4%362.5</t>
+          <t>-0.73%270.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>362.5</v>
+        <v>270.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.36%1,751,000</t>
+          <t>1.37%2,410,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1751000</v>
+        <v>2410000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+6.76%695</t>
+          <t>-2.39%184</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+6.76%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>695</v>
+        <v>184</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.32%933,000</t>
+          <t>1.35%3,439,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>933000</v>
+        <v>3439000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+7.99%17295</t>
+          <t>-5.38%343</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+7.99%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>17295</v>
+        <v>343</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.25%35,900</t>
+          <t>1.32%1,751,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>35900</v>
+        <v>1751000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.13%92.3</t>
+          <t>-1.82%16980</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>92.3</v>
+        <v>16980</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.25%6,406,000</t>
+          <t>1.30%35,900</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>6406000</v>
+        <v>35900</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:55</t>
+          <t>2026-10-29 23:20:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+8.19%1585</t>
+          <t>-2.52%1545</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1585</v>
+        <v>1545</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.22%382,000</t>
+          <t>1.26%382,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.27%248</t>
+          <t>-2.71%89.8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>248</v>
+        <v>89.8</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.21%2,287,000</t>
+          <t>1.23%6,406,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>2287000</v>
+        <v>6406000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+7.42%1375</t>
+          <t>+1.09%1390</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+7.42%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1375</v>
+        <v>1390</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.17%421,000</t>
+          <t>1.21%421,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+7.07%272.5</t>
+          <t>-2.22%242.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+7.07%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>272.5</v>
+        <v>242.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.06%1,910,000</t>
+          <t>1.18%2,287,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1910000</v>
+        <v>2287000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+5.51%479</t>
+          <t>-10%2880</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+5.51%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>479</v>
+        <v>2880</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.99%1,000,000</t>
+          <t>1.00%150,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000000</v>
+        <v>150000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+9.97%3200</t>
+          <t>-2.82%465.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3200</v>
+        <v>465.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.95%150,000</t>
+          <t>1.00%1,000,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>150000</v>
+        <v>1000000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.77%1100</t>
+          <t>-5.45%1040</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1100</v>
+        <v>1040</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.63%396</t>
+          <t>-1.01%392</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.90%1,032,000</t>
+          <t>0.85%1,032,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>5536聖暉*</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+3.89%615</t>
+          <t>-0.38%785</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+3.89%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>615</v>
+        <v>785</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.88%683,000</t>
+          <t>0.75%455,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>683000</v>
+        <v>455000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5536聖暉*</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+4.65%788</t>
+          <t>-2.93%597</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+4.65%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>788</v>
+        <v>597</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.75%455,000</t>
+          <t>0.70%549,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>455000</v>
+        <v>549000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+3.5%207</t>
+          <t>-2.9%201</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+3.5%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.70%1,607,000</t>
+          <t>0.69%1,607,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+2.81%51.3</t>
+          <t>-1.17%50.7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.37%592</t>
+          <t>-4.22%567</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.37%</t>
+          <t>-4.22%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>592</v>
+        <v>567</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.39%306,000</t>
+          <t>0.38%306,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+1.51%168.5</t>
+          <t>-5.04%160</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>-5.04%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>168.5</v>
+        <v>160</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.37%1,022,000</t>
+          <t>0.36%1,022,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.27%73</t>
+          <t>+0.55%73.4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.35%2,213,556</t>
+          <t>0.34%2,213,556</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:56</t>
+          <t>2026-10-29 23:20:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+2.84%253.5</t>
+          <t>-2.76%158.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+2.84%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>253.5</v>
+        <v>158.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.34%632,000</t>
+          <t>0.34%990,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>632000</v>
+        <v>990000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+6.54%163</t>
+          <t>-3.75%244</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+6.54%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>163</v>
+        <v>244</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.33%990,000</t>
+          <t>0.33%632,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>990000</v>
+        <v>632000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+4.37%119.5</t>
+          <t>-2.09%117</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>119.5</v>
+        <v>117</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+3.64%114</t>
+          <t>0%114</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+3.64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+4.59%979</t>
+          <t>-3.98%940</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+4.59%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>979</v>
+        <v>940</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.84%1200</t>
+          <t>+3.33%1240</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-4.14%45.15</t>
+          <t>-0.44%44.95</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-4.14%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>45.15</v>
+        <v>44.95</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+9.96%8170</t>
+          <t>-6.49%7640</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-6.49%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8170</v>
+        <v>7640</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>+5.57%2655</t>
+          <t>-4.33%2540</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>+5.57%</t>
+          <t>-4.33%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2655</v>
+        <v>2540</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-0.9%165.5</t>
+          <t>-0.91%164</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>165.5</v>
+        <v>164</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+9.39%460</t>
+          <t>-4.67%438.5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+9.39%</t>
+          <t>-4.67%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>460</v>
+        <v>438.5</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+1.2%592</t>
+          <t>-4.9%563</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-2%53.9</t>
+          <t>+1.67%54.8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>53.9</v>
+        <v>54.8</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-29 00:02:57</t>
+          <t>2026-10-29 23:20:05</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3986,16 +3986,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-0.62%161</t>
+          <t>+0.62%162</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-29_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
